--- a/training_survey_templates/031_pet_training_program_satisfaction_survey--training_survey_templates.xlsx
+++ b/training_survey_templates/031_pet_training_program_satisfaction_survey--training_survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_'1'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': '1'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_'2'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': '2'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied',_'value':_'3'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied', 'value': '3'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied',_'value':_'4'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied', 'value': '4'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'google_search',_'value':_'google'}</t>
+          <t>google_search</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Google Search', 'value': 'google'}</t>
+          <t>Google Search</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'facebook',_'value':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook', 'value': 'facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'instagram',_'value':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram', 'value': 'instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'referral',_'value':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Referral', 'value': 'referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_years',_'value':_'1-2'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '1-2 years', 'value': '1-2'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_years',_'value':_'2-5'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '2-5 years', 'value': '2-5'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'5+_years',_'value':_'5+'}</t>
+          <t>5+_years</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '5+ years', 'value': '5+'}</t>
+          <t>5+ years</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Monday', 'value': 'monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday', 'value': 'tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday', 'value': 'wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday', 'value': 'thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Friday', 'value': 'friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday', 'value': 'saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday', 'value': 'sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
